--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486887_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486887_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4672</v>
+        <v>7.0972</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1864</v>
+        <v>4.6978</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2808</v>
+        <v>2.3993</v>
       </c>
       <c r="G2" t="n">
         <v>4.3026</v>
@@ -610,13 +610,13 @@
         <v>2.8748</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7845</v>
+        <v>-1.1545</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0462</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7383</v>
+        <v>-0.6197</v>
       </c>
       <c r="V2" t="n">
         <v>1.0743</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.184</v>
+        <v>3.0149</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0328</v>
+        <v>2.4783</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1512</v>
+        <v>0.5366</v>
       </c>
       <c r="G3" t="n">
         <v>4.1345</v>
@@ -688,13 +688,13 @@
         <v>3.0801</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.5443</v>
+        <v>-1.7134</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3756</v>
+        <v>-0.93</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1687</v>
+        <v>-0.7834</v>
       </c>
       <c r="V3" t="n">
         <v>0.5938</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9728</v>
+        <v>2.6695</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2347</v>
+        <v>0.1062</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2075</v>
+        <v>2.5632</v>
       </c>
       <c r="G4" t="n">
         <v>0.9559</v>
@@ -766,13 +766,13 @@
         <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5955</v>
+        <v>-0.8988</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8486</v>
+        <v>-0.5077</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7469</v>
+        <v>-0.3912</v>
       </c>
       <c r="V4" t="n">
         <v>0.3536</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. HALL</t>
+          <t>J. CASTILLO CARRASCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.377</v>
+        <v>0.1039</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7408</v>
+        <v>1.7552</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1179</v>
+        <v>-1.6513</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1993</v>
+        <v>2.2345</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7728</v>
+        <v>-0.594</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4265</v>
+        <v>2.8285</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4906</v>
+        <v>1.9258</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7407</v>
+        <v>0.0973</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7498</v>
+        <v>1.8285</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2913</v>
+        <v>0.3087</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0321</v>
+        <v>-0.6913</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3234</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2588</v>
+        <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2349</v>
+        <v>-0.8</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1513</v>
+        <v>-0.1706</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3861</v>
+        <v>-0.6294</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2357</v>
+        <v>-2.3573</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2357</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CASTILLO CARRASCO</t>
+          <t>J. BOIX COLET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3065</v>
+        <v>0.0179</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8985</v>
+        <v>1.5665</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.592</v>
+        <v>-1.5487</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2345</v>
+        <v>0.4066</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.594</v>
+        <v>0.9699</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8285</v>
+        <v>-0.5632</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9258</v>
+        <v>0.7715</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0973</v>
+        <v>1.5217</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8285</v>
+        <v>-0.7502</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3087</v>
+        <v>-0.3649</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6913</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.187</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5974</v>
+        <v>-0.7913</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0272</v>
+        <v>-0.3836</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5702</v>
+        <v>-0.4076</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.3573</v>
+        <v>-0.8295</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3573</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BOIX COLET</t>
+          <t>S. HALL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0161</v>
+        <v>-0.2587</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3573</v>
+        <v>-1.9616</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3412</v>
+        <v>1.7029</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4066</v>
+        <v>1.1993</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9699</v>
+        <v>0.7728</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5632</v>
+        <v>0.4265</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7715</v>
+        <v>1.4906</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5217</v>
+        <v>0.7407</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7502</v>
+        <v>0.7498</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3649</v>
+        <v>-0.2913</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5518999999999999</v>
+        <v>0.0321</v>
       </c>
       <c r="O7" t="n">
-        <v>0.187</v>
+        <v>-0.3234</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2321</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q7" t="n">
+        <v>-3.0801</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.2588</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.4009</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.3721</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.0289</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.2357</v>
+      </c>
+      <c r="W7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.2321</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.793</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.5928</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.2001</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.8295</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.1786</v>
-      </c>
       <c r="X7" t="n">
-        <v>-2.0082</v>
+        <v>-0.2357</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0095</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4156</v>
+        <v>-1.311</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4061</v>
+        <v>0.3468</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1477</v>
@@ -1078,13 +1078,13 @@
         <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5974</v>
+        <v>-0.5521</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5192</v>
+        <v>-0.4146</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.1374</v>
       </c>
       <c r="V8" t="n">
         <v>-2.1125</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>N. FERRER IGLESIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2358</v>
+        <v>-1.3677</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0852</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.321</v>
+        <v>-0.6273</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6422</v>
+        <v>0.4963</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6028</v>
+        <v>0.3989</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9606</v>
+        <v>0.0973</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1143</v>
+        <v>0.7745</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6355</v>
+        <v>0.8404</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7498</v>
+        <v>-0.0659</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.2783</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9673</v>
+        <v>-0.4415</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2107</v>
+        <v>0.1632</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2321</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8481</v>
+        <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5401</v>
+        <v>-0.864</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2749</v>
+        <v>-0.4882</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.3757</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1786</v>
+        <v>-0.5893</v>
       </c>
       <c r="W9" t="n">
-        <v>3.7761</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.5975</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. FERRER IGLESIA</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4196</v>
+        <v>-1.7243</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9109</v>
+        <v>0.4188</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5087</v>
+        <v>-2.1431</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4963</v>
+        <v>-0.6422</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3989</v>
+        <v>-1.6028</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0973</v>
+        <v>0.9606</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7745</v>
+        <v>0.1143</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8404</v>
+        <v>-0.6355</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0659</v>
+        <v>0.7498</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2783</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4415</v>
+        <v>-0.9673</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1632</v>
+        <v>0.2107</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4107</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R10" t="n">
-        <v>0.616</v>
+        <v>1.8481</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9159</v>
+        <v>-1.0286</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6587</v>
+        <v>-0.3915</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2571</v>
+        <v>-0.6372</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5893</v>
+        <v>1.1786</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.7761</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5893</v>
+        <v>-2.5975</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8739</v>
+        <v>-1.8154</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0606</v>
+        <v>-0.8242</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8133</v>
+        <v>-0.9912</v>
       </c>
       <c r="G11" t="n">
         <v>0.6243</v>
@@ -1312,13 +1312,13 @@
         <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2231</v>
+        <v>-0.1646</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1317</v>
+        <v>0.1046</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.2692</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6591</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.784799999999999</v>
+        <v>6.773099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1976</v>
+        <v>6.185599999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5872999999999998</v>
+        <v>0.5872000000000007</v>
       </c>
       <c r="G12" t="n">
         <v>13.5641</v>
@@ -1360,13 +1360,13 @@
         <v>6.1306</v>
       </c>
       <c r="I12" t="n">
-        <v>7.433399999999999</v>
+        <v>7.4334</v>
       </c>
       <c r="J12" t="n">
         <v>13.7529</v>
       </c>
       <c r="K12" t="n">
-        <v>9.005400000000002</v>
+        <v>9.0054</v>
       </c>
       <c r="L12" t="n">
         <v>4.7475</v>
@@ -1381,7 +1381,7 @@
         <v>2.6859</v>
       </c>
       <c r="P12" t="n">
-        <v>6.160299999999999</v>
+        <v>6.1603</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.2937</v>
@@ -1390,13 +1390,13 @@
         <v>17.4542</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.356300000000001</v>
+        <v>-8.3682</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.0764</v>
+        <v>-4.088500000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.279700000000001</v>
+        <v>-4.2797</v>
       </c>
       <c r="V12" t="n">
         <v>-4.5831</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2819</v>
+        <v>5.2209</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8436</v>
+        <v>3.6344</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4383</v>
+        <v>1.5865</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4228</v>
@@ -1468,13 +1468,13 @@
         <v>1.6427</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2223</v>
+        <v>1.1613</v>
       </c>
       <c r="T13" t="n">
-        <v>0.612</v>
+        <v>0.4028</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6103</v>
+        <v>0.7585</v>
       </c>
       <c r="V13" t="n">
         <v>5.3038</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9034</v>
+        <v>2.5645</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8487</v>
+        <v>1.4889</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0547</v>
+        <v>1.0756</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2137</v>
@@ -1546,13 +1546,13 @@
         <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5976</v>
+        <v>2.2587</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6459</v>
+        <v>1.286</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9517</v>
+        <v>0.9726</v>
       </c>
       <c r="V14" t="n">
         <v>0.1088</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6335</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1844</v>
+        <v>0.9752</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.1743</v>
       </c>
       <c r="G15" t="n">
         <v>0.3566</v>
@@ -1624,13 +1624,13 @@
         <v>1.4374</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0181</v>
+        <v>1.1855</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8832</v>
+        <v>0.674</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1349</v>
+        <v>0.5115</v>
       </c>
       <c r="V15" t="n">
         <v>-1.7679</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.4617</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7215</v>
+        <v>-0.829</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8182</v>
+        <v>1.2907</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.0303</v>
+        <v>-2.4265</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6069</v>
+        <v>-1.8713</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4234</v>
+        <v>-0.5552</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5995</v>
+        <v>-1.3566</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0584</v>
+        <v>-1.2642</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6579</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4308</v>
+        <v>-1.0699</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6653</v>
+        <v>-0.6071</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.4629</v>
       </c>
       <c r="P16" t="n">
-        <v>0.616</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.4374</v>
       </c>
       <c r="R16" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0774</v>
+        <v>1.4693</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0808</v>
+        <v>0.5461</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0034</v>
+        <v>0.9232</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2402</v>
+        <v>1.4189</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2402</v>
+        <v>1.4189</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7834</v>
+        <v>-0.346</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7169</v>
+        <v>0.3031</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.6491</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.8253</v>
+        <v>-2.0303</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6935</v>
+        <v>-0.6069</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1318</v>
+        <v>-1.4234</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2841</v>
+        <v>-0.5995</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.639</v>
+        <v>0.0584</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3548</v>
+        <v>-0.6579</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5412</v>
+        <v>-1.4308</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0546</v>
+        <v>-0.6653</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4866</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1922</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3875</v>
+        <v>0.6624</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1953</v>
+        <v>0.1657</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4661</v>
+        <v>0.2402</v>
       </c>
       <c r="W17" t="n">
-        <v>2.0082</v>
+        <v>0.2402</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-0.4557</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0842</v>
+        <v>-0.5077</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2994</v>
+        <v>0.052</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4265</v>
+        <v>-1.8253</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8713</v>
+        <v>-1.6935</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5552</v>
+        <v>-0.1318</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3566</v>
+        <v>-0.2841</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2642</v>
+        <v>-0.639</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.09229999999999999</v>
+        <v>0.3548</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0699</v>
+        <v>-1.5412</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6071</v>
+        <v>-1.0546</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4629</v>
+        <v>-0.4866</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.4374</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2228</v>
+        <v>0.1356</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7091</v>
+        <v>-0.1783</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.3139</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4189</v>
+        <v>2.4661</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4189</v>
+        <v>2.0082</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9939</v>
+        <v>-0.6313</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7044</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6983</v>
+        <v>-1.4403</v>
       </c>
       <c r="G19" t="n">
         <v>1.0166</v>
@@ -1936,13 +1936,13 @@
         <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1948</v>
+        <v>1.5575</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5538</v>
+        <v>0.6584</v>
       </c>
       <c r="U19" t="n">
-        <v>0.641</v>
+        <v>0.899</v>
       </c>
       <c r="V19" t="n">
         <v>-1.7679</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>J. SOLER CIRUJEDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4263</v>
+        <v>-3.041</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5781</v>
+        <v>0.0166</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8482</v>
+        <v>-3.0576</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7437</v>
+        <v>-2.1208</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1571</v>
+        <v>0.5709</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5866</v>
+        <v>-2.6917</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1182</v>
+        <v>0.8489</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1577</v>
+        <v>2.1252</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0395</v>
+        <v>-1.2763</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6255</v>
+        <v>-2.9697</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9994</v>
+        <v>-1.5543</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6261</v>
+        <v>-1.4154</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.6694</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8082</v>
+        <v>0.587</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4416</v>
+        <v>0.0425</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3666</v>
+        <v>0.5445</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1786</v>
+        <v>-0.4805</v>
       </c>
       <c r="W20" t="n">
         <v>1.1786</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SOLER CIRUJEDA</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4908</v>
+        <v>-3.8587</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.611</v>
+        <v>-2.8919</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8797</v>
+        <v>-0.9668</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1208</v>
+        <v>-2.7437</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5709</v>
+        <v>-2.1571</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6917</v>
+        <v>-0.5866</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8489</v>
+        <v>-1.1182</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1252</v>
+        <v>-1.1577</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2763</v>
+        <v>0.0395</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9697</v>
+        <v>-1.6255</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5543</v>
+        <v>-0.9994</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4154</v>
+        <v>-0.6261</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0267</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1372</v>
+        <v>0.3758</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5851</v>
+        <v>0.1278</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.248</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.4805</v>
+        <v>1.1786</v>
       </c>
       <c r="W21" t="n">
         <v>1.1786</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.6591</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0278</v>
+        <v>-5.8029</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8997</v>
+        <v>-3.5858</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1281</v>
+        <v>-2.217</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1541</v>
@@ -2170,13 +2170,13 @@
         <v>0.2053</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2701</v>
+        <v>0.495</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2558</v>
+        <v>0.058</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5258</v>
+        <v>0.4369</v>
       </c>
       <c r="V22" t="n">
         <v>-2.117</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7849</v>
+        <v>-5.0876</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5873000000000008</v>
+        <v>-0.5872000000000006</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.1976</v>
+        <v>-4.5003</v>
       </c>
       <c r="G23" t="n">
         <v>-13.564</v>
@@ -2248,16 +2248,16 @@
         <v>11.2938</v>
       </c>
       <c r="S23" t="n">
-        <v>9.356299999999999</v>
+        <v>10.0538</v>
       </c>
       <c r="T23" t="n">
-        <v>4.2798</v>
+        <v>4.279699999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>5.0765</v>
+        <v>5.7738</v>
       </c>
       <c r="V23" t="n">
-        <v>4.583099999999999</v>
+        <v>4.5831</v>
       </c>
       <c r="W23" t="n">
         <v>12.398</v>
